--- a/public/database/Clientes.xlsx
+++ b/public/database/Clientes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ignacio Aguilera\Desktop\Trabajo (SPA)\ProyectoReact\public\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D42029AA-325E-4E84-9F3D-36172786CFFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EC47D5D-E5A5-4AFA-A0BE-2B387ED11D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Usuarios" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="67">
   <si>
     <t>idCliente</t>
   </si>
@@ -58,6 +58,24 @@
     <t>logoCliente</t>
   </si>
   <si>
+    <t>Suscripcion</t>
+  </si>
+  <si>
+    <t>tbk_user</t>
+  </si>
+  <si>
+    <t>tarjeta</t>
+  </si>
+  <si>
+    <t>tipo_tarjeta</t>
+  </si>
+  <si>
+    <t>entorno_tbk</t>
+  </si>
+  <si>
+    <t>clienteInternacional</t>
+  </si>
+  <si>
     <t>Mi amorcito</t>
   </si>
   <si>
@@ -73,12 +91,24 @@
     <t>$10.000</t>
   </si>
   <si>
-    <t>2025-08-04</t>
+    <t>2025-11-09</t>
   </si>
   <si>
     <t>https://www.ivelpink.cl/logo-ivelpink-correo.png</t>
   </si>
   <si>
+    <t>cb47a9ea-308b-487b-8dda-8019f9273b43</t>
+  </si>
+  <si>
+    <t>XXXXXXXXXXXX5743</t>
+  </si>
+  <si>
+    <t>Prepago</t>
+  </si>
+  <si>
+    <t>PRODUCCION</t>
+  </si>
+  <si>
     <t>Matias Aguilera</t>
   </si>
   <si>
@@ -91,7 +121,7 @@
     <t>aguilera.matias.salinas@gmail.com</t>
   </si>
   <si>
-    <t>2025-08-01</t>
+    <t/>
   </si>
   <si>
     <t>https://masautomatizacion.cl/logo-masautomatizacion.jpg</t>
@@ -118,9 +148,6 @@
     <t>Sntcontactos@gmail.com</t>
   </si>
   <si>
-    <t>2025-08-07</t>
-  </si>
-  <si>
     <t>https://ingsnt.cl/logo-ingsnt-correo-white.webp</t>
   </si>
   <si>
@@ -130,9 +157,6 @@
     <t>www.mastracker.cl</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>https://mastracker.cl/logo-masautomatizacion.jpg</t>
   </si>
   <si>
@@ -148,32 +172,68 @@
     <t>ag.investigadoresprivados@gmail.com</t>
   </si>
   <si>
-    <t>https://investigadores-privados.cl/logo-investigaciones-1.png</t>
+    <t>https://investigadores-privados.cl/logo-investigadores.jpg</t>
+  </si>
+  <si>
+    <t>Javier</t>
+  </si>
+  <si>
+    <t>reparamostucelular.com</t>
+  </si>
+  <si>
+    <t>www.reparamostucelular.com</t>
+  </si>
+  <si>
+    <t>servicio@reparamostucelular.com</t>
+  </si>
+  <si>
+    <t>www.reparamostucelular.netlify.app/logo-reparamostucelular.png</t>
+  </si>
+  <si>
+    <t>Ignacio Aguilera</t>
+  </si>
+  <si>
+    <t>plataformas-web.cl</t>
+  </si>
+  <si>
+    <t>www.plataformas-web.cl</t>
+  </si>
+  <si>
+    <t>aguileraignacio1992@gmail.com</t>
+  </si>
+  <si>
+    <t>2026-02-14</t>
+  </si>
+  <si>
+    <t>https://plataformas-web.cl/logo-plataformas-web-correo.webp</t>
+  </si>
+  <si>
+    <t>53308411-7fbf-47bc-8a2f-b165eda51a47</t>
+  </si>
+  <si>
+    <t>XXXXXXXXXXXX6404</t>
+  </si>
+  <si>
+    <t>RedCompra</t>
+  </si>
+  <si>
+    <t>Cliente Internacional</t>
+  </si>
+  <si>
+    <t>plataformas-web.com</t>
+  </si>
+  <si>
+    <t>www.plataformas-web.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -187,20 +247,15 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -208,36 +263,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Accent1" xfId="1" builtinId="29"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -251,6 +287,32 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6C38BC2B-0BD4-4D1B-9FE4-5E46D14CC683}" name="Table1" displayName="Table1" ref="A1:Q10" totalsRowShown="0">
+  <autoFilter ref="A1:Q10" xr:uid="{6C38BC2B-0BD4-4D1B-9FE4-5E46D14CC683}"/>
+  <tableColumns count="17">
+    <tableColumn id="1" xr3:uid="{5CADBF12-350A-4F5C-9502-82BA30D89455}" name="idCliente"/>
+    <tableColumn id="2" xr3:uid="{AB22BCD9-8A3C-4BB6-8200-95FCE93FFADB}" name="cliente"/>
+    <tableColumn id="3" xr3:uid="{71BBF236-AEFE-4672-9BDD-B4600D0CAF6B}" name="sitioWeb"/>
+    <tableColumn id="4" xr3:uid="{6CFD9028-3FD6-4052-A8CB-FCCD228FD467}" name="URL"/>
+    <tableColumn id="5" xr3:uid="{51141BA4-3155-4A83-876F-802EFAA71353}" name="telefono"/>
+    <tableColumn id="6" xr3:uid="{CD832B9F-5969-4654-8CC3-7CACA74DADAC}" name="correo"/>
+    <tableColumn id="7" xr3:uid="{0BEC0FB7-F1D7-41B1-A131-0C2761608A98}" name="pagado"/>
+    <tableColumn id="8" xr3:uid="{6D51EEC8-37A7-4B3A-AB36-A4CF83148436}" name="valor"/>
+    <tableColumn id="9" xr3:uid="{D37F9BAA-9D19-4F87-8FBB-D3CE75A7DE64}" name="fechaPago"/>
+    <tableColumn id="10" xr3:uid="{CA72C604-97F4-4A6B-A0C7-567895A628C9}" name="estado"/>
+    <tableColumn id="11" xr3:uid="{113C2A44-004B-43AA-9C04-E1A163957DF1}" name="logoCliente"/>
+    <tableColumn id="12" xr3:uid="{A9812EFF-CF53-42C6-B71A-455C65CF8F26}" name="Suscripcion"/>
+    <tableColumn id="13" xr3:uid="{675C278E-E1E5-490D-B647-EF8B72B89B05}" name="tbk_user"/>
+    <tableColumn id="14" xr3:uid="{5EED195B-69B7-43A7-BE9C-0255E5830D92}" name="tarjeta"/>
+    <tableColumn id="15" xr3:uid="{D7666A72-8E61-407D-A7D9-ADE5FF3F73B3}" name="tipo_tarjeta"/>
+    <tableColumn id="16" xr3:uid="{CE653D68-3EA2-473F-91FB-C6177A33E538}" name="entorno_tbk"/>
+    <tableColumn id="17" xr3:uid="{DFFCC460-467C-43C6-9BE2-79B6C159A90C}" name="clienteInternacional"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -550,274 +612,544 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.09765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.09765625" customWidth="1"/>
+    <col min="2" max="2" width="18.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.8984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27.69921875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.8984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="33.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.59765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.69921875" customWidth="1"/>
-    <col min="9" max="9" width="10.09765625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="51" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.09765625" customWidth="1"/>
+    <col min="11" max="11" width="12.09765625" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="9.8984375" customWidth="1"/>
+    <col min="15" max="15" width="12.59765625" customWidth="1"/>
+    <col min="16" max="16" width="13.09765625" customWidth="1"/>
+    <col min="17" max="17" width="19.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+    <row r="1" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="1">
+    <row r="2" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2">
         <v>56936300432</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="1">
-        <v>1</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>17</v>
+      <c r="F2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O2" t="s">
+        <v>26</v>
+      </c>
+      <c r="P2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
+    <row r="3" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="1">
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3">
         <v>56922292189</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="1">
-        <v>1</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J3" s="1">
-        <v>1</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>23</v>
+      <c r="I3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P3" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
+    <row r="4" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="1">
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4">
         <v>56922292189</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="1">
-        <v>1</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" s="1">
-        <v>1</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>26</v>
+      <c r="I4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>36</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N4" t="s">
+        <v>32</v>
+      </c>
+      <c r="O4" t="s">
+        <v>32</v>
+      </c>
+      <c r="P4" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
+    <row r="5" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5">
+        <v>56999440746</v>
+      </c>
+      <c r="F5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5" t="s">
+        <v>41</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5" t="s">
+        <v>32</v>
+      </c>
+      <c r="N5" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" t="s">
+        <v>32</v>
+      </c>
+      <c r="P5" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6">
+        <v>56922292189</v>
+      </c>
+      <c r="F6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6" t="s">
+        <v>44</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N6" t="s">
+        <v>32</v>
+      </c>
+      <c r="O6" t="s">
+        <v>32</v>
+      </c>
+      <c r="P6" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7">
+        <v>56946873014</v>
+      </c>
+      <c r="F7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7" t="s">
+        <v>32</v>
+      </c>
+      <c r="N7" t="s">
+        <v>32</v>
+      </c>
+      <c r="O7" t="s">
+        <v>32</v>
+      </c>
+      <c r="P7" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8">
+        <v>17873738888</v>
+      </c>
+      <c r="F8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8" t="s">
+        <v>54</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="P8" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="1">
-        <v>56999440746</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J5" s="1">
-        <v>1</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>32</v>
+      <c r="Q8">
+        <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="1">
-        <v>56922292189</v>
-      </c>
-      <c r="F6" s="1" t="s">
+    <row r="9" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9">
+        <v>56992914526</v>
+      </c>
+      <c r="F9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="1">
-        <v>0</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="J6" s="1">
-        <v>1</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>36</v>
+      <c r="I9" t="s">
+        <v>59</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9" t="s">
+        <v>60</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9" t="s">
+        <v>61</v>
+      </c>
+      <c r="N9" t="s">
+        <v>62</v>
+      </c>
+      <c r="O9" t="s">
+        <v>63</v>
+      </c>
+      <c r="P9" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="1">
-        <v>56946873014</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="J7" s="1">
-        <v>1</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>41</v>
+    <row r="10" spans="1:17" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10">
+        <v>56992914526</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" t="s">
+        <v>59</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10" t="s">
+        <v>60</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="P10" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
-    <hyperlink ref="D7" r:id="rId1" xr:uid="{8D3D9A9A-08AD-419A-9244-CCF4EBAD9106}"/>
-    <hyperlink ref="K7" r:id="rId2" xr:uid="{E85EC306-C209-4A28-8E14-C398A4AD483F}"/>
+    <hyperlink ref="D10" r:id="rId1" xr:uid="{623F1EB1-49B2-4350-A1B4-ED7ECDE57D4D}"/>
+    <hyperlink ref="F10" r:id="rId2" xr:uid="{A4C22D58-BF9E-4CA5-8AA3-770367597B9D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:K6" numberStoredAsText="1"/>
-  </ignoredErrors>
+  <tableParts count="1">
+    <tablePart r:id="rId3"/>
+  </tableParts>
 </worksheet>
 </file>